--- a/laporan_padel_dki_jakarta_2026-10-31.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-31.xlsx
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.730.000</t>
+          <t>Rp16.925.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.775.000</t>
+          <t>Rp9.124.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.039.500</t>
+          <t>Rp1.155.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.880.000</t>
+          <t>Rp4.435.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-31.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-31.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp770.000</t>
+          <t>Rp840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp948.000</t>
+          <t>Rp1.073.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp968.000</t>
+          <t>Rp1.056.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp21.310.000</t>
+          <t>Rp20.560.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.650.000</t>
+          <t>Rp17.062.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.233.000</t>
+          <t>Rp4.731.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.390.000</t>
+          <t>Rp790.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.938.000</t>
+          <t>Rp2.864.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp18.210.000</t>
+          <t>Rp18.595.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.665.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.113.000</t>
+          <t>Rp1.313.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>34</v>
       </c>
       <c r="D65" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.795.000</t>
+          <t>Rp2.275.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.890.000</t>
+          <t>Rp4.695.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.287.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp5.410.000</t>
+          <t>Rp5.490.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.850.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.558.000</t>
+          <t>Rp9.336.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.638.000</t>
+          <t>Rp2.763.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.680.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp14.450.000</t>
+          <t>Rp14.700.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>28</v>
       </c>
       <c r="D36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp756.000</t>
+          <t>Rp567.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp10.650.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp456.000</t>
+          <t>Rp529.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>51</v>
       </c>
       <c r="D58" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp660.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>64</v>
       </c>
       <c r="D63" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp299.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.678.000</t>
+          <t>Rp5.942.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.800.000</t>
+          <t>Rp10.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp27.950.000</t>
+          <t>Rp29.700.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.835.000</t>
+          <t>Rp3.935.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6443,16 +6443,16 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6474,16 +6474,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6505,16 +6505,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp188.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp8.530.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp69.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.925.000</t>
+          <t>Rp17.105.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.124.000</t>
+          <t>Rp8.874.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.175.000</t>
+          <t>Rp18.225.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.008.000</t>
+          <t>Rp3.196.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp376.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp24.998.000</t>
+          <t>Rp25.297.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.612.000</t>
+          <t>Rp3.741.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.420.000</t>
+          <t>Rp13.690.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp597.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp5.382.000</t>
+          <t>Rp4.186.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.210.000</t>
+          <t>Rp2.730.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp7.599.962</t>
+          <t>Rp7.999.960</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.772.000</t>
+          <t>Rp2.871.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.435.000</t>
+          <t>Rp3.990.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.510.000</t>
+          <t>Rp7.560.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.110.000</t>
+          <t>Rp1.295.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-31.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-31.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.073.000</t>
+          <t>Rp1.323.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.356.000</t>
+          <t>Rp4.554.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp20.560.000</t>
+          <t>Rp19.810.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.062.500</t>
+          <t>Rp17.722.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp790.000</t>
+          <t>Rp940.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>102</v>
       </c>
       <c r="D31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.660.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.042.000</t>
+          <t>Rp1.672.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.165.000</t>
+          <t>Rp6.290.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.864.000</t>
+          <t>Rp3.222.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.645.000</t>
+          <t>Rp3.735.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp14.729.000</t>
+          <t>Rp15.327.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.900.000</t>
+          <t>Rp9.300.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp3.636.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.955.000</t>
+          <t>Rp2.105.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.410.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.695.000</t>
+          <t>Rp5.185.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.325.000</t>
+          <t>Rp1.775.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.257.000</t>
+          <t>Rp4.455.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.287.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp100.000</t>
+          <t>Rp249.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp4.752.000</t>
+          <t>Rp3.696.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp4.850.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.576.500</t>
+          <t>Rp17.104.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.500.000</t>
+          <t>Rp12.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.685.000</t>
+          <t>Rp4.035.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.895.000</t>
+          <t>Rp3.195.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.560.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.920.000</t>
+          <t>Rp8.415.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp14.700.000</t>
+          <t>Rp14.900.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp10.780.000</t>
+          <t>Rp10.910.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp19.350.000</t>
+          <t>Rp19.750.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp9.900.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp6.710.000</t>
+          <t>Rp6.985.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp529.000</t>
+          <t>Rp618.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp660.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>34</v>
       </c>
       <c r="D64" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp299.000</t>
+          <t>Rp598.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp5.942.000</t>
+          <t>Rp6.092.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5772,16 +5772,16 @@
         <v>34</v>
       </c>
       <c r="D70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.455.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.700.000</t>
+          <t>Rp30.635.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.313.000</t>
+          <t>Rp1.711.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.935.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp8.530.000</t>
+          <t>Rp8.760.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp69.000</t>
+          <t>Rp276.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.874.000</t>
+          <t>Rp9.124.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.316.000</t>
+          <t>Rp1.692.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.350.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.750.000</t>
+          <t>Rp17.950.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.966.000</t>
+          <t>Rp7.128.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>68</v>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.751.000</t>
+          <t>Rp5.905.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.070.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.225.000</t>
+          <t>Rp18.375.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp25.297.000</t>
+          <t>Rp25.895.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp3.741.000</t>
+          <t>Rp4.128.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>102</v>
       </c>
       <c r="D51" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.690.000</t>
+          <t>Rp14.030.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp4.186.000</t>
+          <t>Rp4.784.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp520.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp13.465.000</t>
+          <t>Rp14.025.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp125.000</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.155.000</t>
+          <t>Rp1.617.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.871.000</t>
+          <t>Rp3.069.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp30.600.000</t>
+          <t>Rp31.080.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>68</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.755.000</t>
+          <t>Rp5.845.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp169.000</t>
+          <t>Rp169.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -9490,16 +9490,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp5.990.000</t>
+          <t>Rp6.870.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-31.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-31.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.925.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.722.500</t>
+          <t>Rp18.075.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.675.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp4.610.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.851.000</t>
+          <t>Rp2.069.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.731.000</t>
+          <t>Rp4.233.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.035.000</t>
+          <t>Rp15.865.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp17.990.000</t>
+          <t>Rp17.492.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.483.000</t>
+          <t>Rp2.322.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.480.000</t>
+          <t>Rp4.640.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.222.000</t>
+          <t>Rp2.148.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp4.518.000</t>
+          <t>Rp3.738.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp15.327.000</t>
+          <t>Rp16.523.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp18.595.000</t>
+          <t>Rp21.545.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp10.950.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>30</v>
       </c>
       <c r="D46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.275.000</t>
+          <t>Rp6.520.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.744.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp175.000</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp894.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp465.000</t>
+          <t>Rp610.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.313.000</t>
+          <t>Rp1.949.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>32</v>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp225.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp9.495.000</t>
+          <t>Rp10.093.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>41</v>
       </c>
       <c r="D68" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp5.980.000</t>
+          <t>Rp5.830.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.105.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>128</v>
       </c>
       <c r="D78" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp5.185.000</t>
+          <t>Rp5.675.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.775.000</t>
+          <t>Rp2.225.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.455.000</t>
+          <t>Rp4.752.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.696.000</t>
+          <t>Rp4.224.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp5.490.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>90</v>
       </c>
       <c r="D94" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>68</v>
       </c>
       <c r="D99" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3582,16 +3582,16 @@
         <v>36</v>
       </c>
       <c r="D102" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp9.336.000</t>
+          <t>Rp10.892.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.200.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.195.000</t>
+          <t>Rp3.395.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp8.750.000</t>
+          <t>Rp9.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>45</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp8.415.000</t>
+          <t>Rp7.920.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>54</v>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp14.900.000</t>
+          <t>Rp15.300.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.540.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp32.480.000</t>
+          <t>Rp33.215.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp19.750.000</t>
+          <t>Rp20.450.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.900.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.800.000</t>
+          <t>Rp9.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>32</v>
       </c>
       <c r="D48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp11.125.000</t>
+          <t>Rp11.475.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp5.373.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>112</v>
       </c>
       <c r="D56" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp618.000</t>
+          <t>Rp764.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.320.000</t>
+          <t>Rp12.705.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp30.635.000</t>
+          <t>Rp33.635.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6412,16 +6412,16 @@
         <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.485.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.105.000</t>
+          <t>Rp17.675.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.124.000</t>
+          <t>Rp9.249.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp16.225.000</t>
+          <t>Rp16.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.950.000</t>
+          <t>Rp16.750.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>96</v>
       </c>
       <c r="D28" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.905.000</t>
+          <t>Rp6.136.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.070.000</t>
+          <t>Rp3.320.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.375.000</t>
+          <t>Rp19.750.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.196.000</t>
+          <t>Rp3.572.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp7.152.000</t>
+          <t>Rp6.152.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp199.000</t>
+          <t>Rp99.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -7734,16 +7734,16 @@
         <v>180</v>
       </c>
       <c r="D38" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>170</v>
       </c>
       <c r="D41" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp25.895.000</t>
+          <t>Rp26.493.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>102</v>
       </c>
       <c r="D47" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8075,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8106,16 +8106,16 @@
         <v>102</v>
       </c>
       <c r="D50" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.128.000</t>
+          <t>Rp4.257.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>102</v>
       </c>
       <c r="D51" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.650.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8199,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.030.000</t>
+          <t>Rp14.920.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.710.000</t>
+          <t>Rp3.945.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp520.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.730.000</t>
+          <t>Rp3.510.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.617.000</t>
+          <t>Rp1.732.500</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.090.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.990.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>144</v>
       </c>
       <c r="D22" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp7.560.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.475.000</t>
+          <t>Rp1.913.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.205.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.845.000</t>
+          <t>Rp6.170.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>136</v>
       </c>
       <c r="D34" t="n">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp11.120.000</t>
+          <t>Rp5.660.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>51</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp3.915.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>90</v>
       </c>
       <c r="D39" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.860.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-31.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-31.xlsx
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp18.075.500</t>
+          <t>Rp18.405.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>117</v>
       </c>
       <c r="D18" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.069.000</t>
+          <t>Rp2.227.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.780.000</t>
+          <t>Rp4.716.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp16.523.000</t>
+          <t>Rp16.723.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp21.545.000</t>
+          <t>Rp22.095.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp75.000</t>
+          <t>Rp70.000 - Rp75.000</t>
         </is>
       </c>
     </row>
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.104.500</t>
+          <t>Rp17.280.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.040.000</t>
+          <t>Rp5.840.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>36</v>
       </c>
       <c r="D62" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5834,16 +5834,16 @@
         <v>162</v>
       </c>
       <c r="D72" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp48.600.000</t>
+          <t>Rp49.300.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.128.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp19.750.000</t>
+          <t>Rp19.950.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.572.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.069.000</t>
+          <t>Rp3.168.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D37" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.550.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.220.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
